--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/20.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/20.xlsx
@@ -426,13 +426,13 @@
         <v>-13.56031299581512</v>
       </c>
       <c r="E2">
-        <v>-25.90218960100689</v>
+        <v>-26.95049510599052</v>
       </c>
       <c r="F2">
-        <v>-4.057425694532363</v>
+        <v>-4.381274273922025</v>
       </c>
       <c r="G2">
-        <v>-18.16858367969141</v>
+        <v>-18.59375452569958</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.06880088542843</v>
       </c>
       <c r="E3">
-        <v>-25.77116273406896</v>
+        <v>-26.64268567074114</v>
       </c>
       <c r="F3">
-        <v>-4.115898492761175</v>
+        <v>-4.504930474709727</v>
       </c>
       <c r="G3">
-        <v>-17.76748551565411</v>
+        <v>-17.87507020814518</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.52065027172488</v>
       </c>
       <c r="E4">
-        <v>-26.07340214628889</v>
+        <v>-29.10241236901345</v>
       </c>
       <c r="F4">
-        <v>-3.921041628600647</v>
+        <v>-4.218307898034472</v>
       </c>
       <c r="G4">
-        <v>-17.51230655558687</v>
+        <v>-18.82457861874184</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.0096916029192</v>
       </c>
       <c r="E5">
-        <v>-26.68367741745858</v>
+        <v>-28.47481115629041</v>
       </c>
       <c r="F5">
-        <v>-4.006199454343242</v>
+        <v>-4.205566779012013</v>
       </c>
       <c r="G5">
-        <v>-17.74468102581597</v>
+        <v>-17.55230792761806</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.58296447112861</v>
       </c>
       <c r="E6">
-        <v>-27.04897130176131</v>
+        <v>-29.35041424804351</v>
       </c>
       <c r="F6">
-        <v>-3.983585024246815</v>
+        <v>-4.132448445101706</v>
       </c>
       <c r="G6">
-        <v>-17.61905617719107</v>
+        <v>-18.38424524790747</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.27172459048197</v>
       </c>
       <c r="E7">
-        <v>-27.8803447878815</v>
+        <v>-30.44180365473612</v>
       </c>
       <c r="F7">
-        <v>-3.81872085863945</v>
+        <v>-3.95361469161353</v>
       </c>
       <c r="G7">
-        <v>-17.35484729539224</v>
+        <v>-17.53684188979762</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.12416991334669</v>
       </c>
       <c r="E8">
-        <v>-28.40764482980864</v>
+        <v>-29.69639871917754</v>
       </c>
       <c r="F8">
-        <v>-3.69750337148559</v>
+        <v>-4.150946717573622</v>
       </c>
       <c r="G8">
-        <v>-17.23066126242115</v>
+        <v>-17.52435027932081</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.17110818934521</v>
       </c>
       <c r="E9">
-        <v>-28.46144762949378</v>
+        <v>-30.52210029160312</v>
       </c>
       <c r="F9">
-        <v>-3.629607065682531</v>
+        <v>-3.966421251660809</v>
       </c>
       <c r="G9">
-        <v>-17.02243822348035</v>
+        <v>-18.2928583056446</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.39806131247892</v>
       </c>
       <c r="E10">
-        <v>-29.40995009582236</v>
+        <v>-29.65230043929085</v>
       </c>
       <c r="F10">
-        <v>-3.515107638165375</v>
+        <v>-3.852431270096375</v>
       </c>
       <c r="G10">
-        <v>-16.62099224995775</v>
+        <v>-17.15686494893846</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.81704621823041</v>
       </c>
       <c r="E11">
-        <v>-29.34723073081612</v>
+        <v>-31.60414292794389</v>
       </c>
       <c r="F11">
-        <v>-3.767490476613314</v>
+        <v>-3.448146559160077</v>
       </c>
       <c r="G11">
-        <v>-16.20243142478108</v>
+        <v>-17.6581798224551</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.39898441404002</v>
       </c>
       <c r="E12">
-        <v>-30.26150699059473</v>
+        <v>-32.3828095050888</v>
       </c>
       <c r="F12">
-        <v>-3.556251818695023</v>
+        <v>-3.517827168348766</v>
       </c>
       <c r="G12">
-        <v>-16.33663666778393</v>
+        <v>-18.0732264593416</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.08791540788606</v>
       </c>
       <c r="E13">
-        <v>-30.87410310469335</v>
+        <v>-32.1931185216185</v>
       </c>
       <c r="F13">
-        <v>-3.497369806969229</v>
+        <v>-3.209030024667971</v>
       </c>
       <c r="G13">
-        <v>-15.6667342711538</v>
+        <v>-16.25663228311077</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.85376468659844</v>
       </c>
       <c r="E14">
-        <v>-30.96688021592549</v>
+        <v>-32.92126770697084</v>
       </c>
       <c r="F14">
-        <v>-3.408505865466509</v>
+        <v>-3.061810913107637</v>
       </c>
       <c r="G14">
-        <v>-15.45004732120041</v>
+        <v>-17.50726495866078</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.62876383420929</v>
       </c>
       <c r="E15">
-        <v>-31.87241425663229</v>
+        <v>-33.90412996983262</v>
       </c>
       <c r="F15">
-        <v>-3.159455549080032</v>
+        <v>-2.775579325846505</v>
       </c>
       <c r="G15">
-        <v>-14.61169357215151</v>
+        <v>-15.24320567653613</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.34709184060034</v>
       </c>
       <c r="E16">
-        <v>-31.92386224983343</v>
+        <v>-34.65730576678836</v>
       </c>
       <c r="F16">
-        <v>-3.292631348060706</v>
+        <v>-2.906944313684659</v>
       </c>
       <c r="G16">
-        <v>-14.57303257912735</v>
+        <v>-16.06510409946442</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.96562156159281</v>
       </c>
       <c r="E17">
-        <v>-33.15460865140108</v>
+        <v>-34.7608810242918</v>
       </c>
       <c r="F17">
-        <v>-2.993502908705388</v>
+        <v>-3.016844645381472</v>
       </c>
       <c r="G17">
-        <v>-14.03788503011127</v>
+        <v>-15.74279790873407</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.42217956300017</v>
       </c>
       <c r="E18">
-        <v>-33.3908908396993</v>
+        <v>-34.83447551962745</v>
       </c>
       <c r="F18">
-        <v>-3.004267543104767</v>
+        <v>-2.780452611277174</v>
       </c>
       <c r="G18">
-        <v>-13.89327503354342</v>
+        <v>-16.297698411538</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-16.68321869305929</v>
       </c>
       <c r="E19">
-        <v>-34.86291660063262</v>
+        <v>-36.00834881613277</v>
       </c>
       <c r="F19">
-        <v>-2.809811608767194</v>
+        <v>-2.669479543793736</v>
       </c>
       <c r="G19">
-        <v>-13.37643341960749</v>
+        <v>-15.80304933961937</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-16.73683832996739</v>
       </c>
       <c r="E20">
-        <v>-34.60957791498452</v>
+        <v>-35.15314423554721</v>
       </c>
       <c r="F20">
-        <v>-2.595620649425326</v>
+        <v>-2.454513232562847</v>
       </c>
       <c r="G20">
-        <v>-13.20188555753127</v>
+        <v>-15.37541593683084</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-16.56418809955269</v>
       </c>
       <c r="E21">
-        <v>-35.17521375362359</v>
+        <v>-36.20778960414158</v>
       </c>
       <c r="F21">
-        <v>-2.472139234159615</v>
+        <v>-2.349970781227341</v>
       </c>
       <c r="G21">
-        <v>-13.38647067635783</v>
+        <v>-14.99674656276312</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-16.18961445014449</v>
       </c>
       <c r="E22">
-        <v>-35.79486296598916</v>
+        <v>-37.54959909498434</v>
       </c>
       <c r="F22">
-        <v>-2.405435777416588</v>
+        <v>-2.400868159557551</v>
       </c>
       <c r="G22">
-        <v>-12.93786862719367</v>
+        <v>-15.66721497011226</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-15.64631305223264</v>
       </c>
       <c r="E23">
-        <v>-36.39280720243596</v>
+        <v>-37.36890392513028</v>
       </c>
       <c r="F23">
-        <v>-2.512959523034769</v>
+        <v>-1.312095180013993</v>
       </c>
       <c r="G23">
-        <v>-13.10993916699251</v>
+        <v>-14.80093966620326</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-14.96063985919338</v>
       </c>
       <c r="E24">
-        <v>-36.78216766185246</v>
+        <v>-37.38533549306711</v>
       </c>
       <c r="F24">
-        <v>-2.224041540286358</v>
+        <v>-1.995529765284892</v>
       </c>
       <c r="G24">
-        <v>-12.75901580243146</v>
+        <v>-14.56925261189087</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-14.19795613298945</v>
       </c>
       <c r="E25">
-        <v>-37.13682416071119</v>
+        <v>-37.7286934492767</v>
       </c>
       <c r="F25">
-        <v>-2.147002543458601</v>
+        <v>-1.589720029960039</v>
       </c>
       <c r="G25">
-        <v>-12.80931364771618</v>
+        <v>-14.5660944361399</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-13.41131046584851</v>
       </c>
       <c r="E26">
-        <v>-36.98088842249405</v>
+        <v>-38.94601971812261</v>
       </c>
       <c r="F26">
-        <v>-2.102545721685157</v>
+        <v>-1.419100367638022</v>
       </c>
       <c r="G26">
-        <v>-12.46400117202178</v>
+        <v>-14.60539034553581</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.63803603380241</v>
       </c>
       <c r="E27">
-        <v>-37.17215757915603</v>
+        <v>-38.70453884166358</v>
       </c>
       <c r="F27">
-        <v>-2.195049509555778</v>
+        <v>-1.310503057865812</v>
       </c>
       <c r="G27">
-        <v>-12.80382416404723</v>
+        <v>-14.51863320689331</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.94288217357574</v>
       </c>
       <c r="E28">
-        <v>-37.16682303677499</v>
+        <v>-37.85314270771849</v>
       </c>
       <c r="F28">
-        <v>-2.128133162390231</v>
+        <v>-1.871740197345339</v>
       </c>
       <c r="G28">
-        <v>-12.98942974277878</v>
+        <v>-14.55205244847626</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.35171620855378</v>
       </c>
       <c r="E29">
-        <v>-37.11638942175157</v>
+        <v>-38.42953367212578</v>
       </c>
       <c r="F29">
-        <v>-2.015036160886015</v>
+        <v>-1.465977678962446</v>
       </c>
       <c r="G29">
-        <v>-12.61040599678264</v>
+        <v>-15.27920888009714</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.87638344965661</v>
       </c>
       <c r="E30">
-        <v>-37.06801173392763</v>
+        <v>-37.82478540348246</v>
       </c>
       <c r="F30">
-        <v>-2.306916385466837</v>
+        <v>-1.75430752085487</v>
       </c>
       <c r="G30">
-        <v>-12.61764437154278</v>
+        <v>-14.14468551064964</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.53765286997058</v>
       </c>
       <c r="E31">
-        <v>-37.24449995142857</v>
+        <v>-38.58766572023663</v>
       </c>
       <c r="F31">
-        <v>-2.034553325263373</v>
+        <v>-1.129377211774089</v>
       </c>
       <c r="G31">
-        <v>-12.89725694795242</v>
+        <v>-14.56163033420828</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.31351217510463</v>
       </c>
       <c r="E32">
-        <v>-36.78356922455784</v>
+        <v>-36.81126310735174</v>
       </c>
       <c r="F32">
-        <v>-2.075928620298403</v>
+        <v>-1.623135542621568</v>
       </c>
       <c r="G32">
-        <v>-12.84066900093824</v>
+        <v>-13.97683134055468</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.18645443395206</v>
       </c>
       <c r="E33">
-        <v>-36.67944828593647</v>
+        <v>-38.14345185516522</v>
       </c>
       <c r="F33">
-        <v>-2.078033501868917</v>
+        <v>-1.407716942788751</v>
       </c>
       <c r="G33">
-        <v>-12.41342114168294</v>
+        <v>-14.1266945728392</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.14072495040979</v>
       </c>
       <c r="E34">
-        <v>-35.75087789795266</v>
+        <v>-37.3261687159199</v>
       </c>
       <c r="F34">
-        <v>-2.110489765078004</v>
+        <v>-1.877579359167673</v>
       </c>
       <c r="G34">
-        <v>-12.69080576865372</v>
+        <v>-14.30924205307735</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.13135372829238</v>
       </c>
       <c r="E35">
-        <v>-35.94483923241219</v>
+        <v>-36.03173385590837</v>
       </c>
       <c r="F35">
-        <v>-2.14095711815297</v>
+        <v>-1.956762170833875</v>
       </c>
       <c r="G35">
-        <v>-13.19702934962329</v>
+        <v>-14.95812822561924</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.14062594133322</v>
       </c>
       <c r="E36">
-        <v>-35.48065479696695</v>
+        <v>-35.92229875303901</v>
       </c>
       <c r="F36">
-        <v>-2.170345936869491</v>
+        <v>-1.942634364779129</v>
       </c>
       <c r="G36">
-        <v>-13.11045431877734</v>
+        <v>-13.93913010483666</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.15032974923047</v>
       </c>
       <c r="E37">
-        <v>-35.08614999107774</v>
+        <v>-36.12077497608419</v>
       </c>
       <c r="F37">
-        <v>-2.087263999838312</v>
+        <v>-1.379038863303832</v>
       </c>
       <c r="G37">
-        <v>-12.94977289901133</v>
+        <v>-15.60496035346491</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.12960624111248</v>
       </c>
       <c r="E38">
-        <v>-34.6666004596891</v>
+        <v>-35.76332440876274</v>
       </c>
       <c r="F38">
-        <v>-1.883392013233117</v>
+        <v>-2.168408385514343</v>
       </c>
       <c r="G38">
-        <v>-13.32474105516</v>
+        <v>-14.03061384313554</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.08491005509839</v>
       </c>
       <c r="E39">
-        <v>-34.32955293200921</v>
+        <v>-34.96564276925962</v>
       </c>
       <c r="F39">
-        <v>-1.987921210690178</v>
+        <v>-2.132255946953964</v>
       </c>
       <c r="G39">
-        <v>-13.33235020795635</v>
+        <v>-14.66101689463308</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.01555217121139</v>
       </c>
       <c r="E40">
-        <v>-34.60533699907634</v>
+        <v>-35.99752349901743</v>
       </c>
       <c r="F40">
-        <v>-2.093161975746244</v>
+        <v>-1.88934051955262</v>
       </c>
       <c r="G40">
-        <v>-13.44350158828254</v>
+        <v>-15.55625718185808</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.915333807867716</v>
       </c>
       <c r="E41">
-        <v>-33.06126095244397</v>
+        <v>-34.88308868809979</v>
       </c>
       <c r="F41">
-        <v>-1.974548875706786</v>
+        <v>-1.671300965257345</v>
       </c>
       <c r="G41">
-        <v>-13.43405823263446</v>
+        <v>-14.40661722468621</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.80963632236257</v>
       </c>
       <c r="E42">
-        <v>-32.93535578960871</v>
+        <v>-33.78661606933358</v>
       </c>
       <c r="F42">
-        <v>-1.925960157328178</v>
+        <v>-2.589663859431795</v>
       </c>
       <c r="G42">
-        <v>-13.75072728472569</v>
+        <v>-13.86158171450075</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.705611148459226</v>
       </c>
       <c r="E43">
-        <v>-32.9340493248575</v>
+        <v>-33.99666027923136</v>
       </c>
       <c r="F43">
-        <v>-2.015745243382811</v>
+        <v>-1.734222924806593</v>
       </c>
       <c r="G43">
-        <v>-13.40272584796332</v>
+        <v>-14.55870840640959</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.609588778637649</v>
       </c>
       <c r="E44">
-        <v>-32.55457905267374</v>
+        <v>-33.41798243545018</v>
       </c>
       <c r="F44">
-        <v>-1.866330958205058</v>
+        <v>-1.705501770216729</v>
       </c>
       <c r="G44">
-        <v>-13.26603343901841</v>
+        <v>-14.72468735838332</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.545335700436381</v>
       </c>
       <c r="E45">
-        <v>-31.34941852924944</v>
+        <v>-33.83766102834804</v>
       </c>
       <c r="F45">
-        <v>-2.062977095955633</v>
+        <v>-2.172546909058729</v>
       </c>
       <c r="G45">
-        <v>-13.57487185585803</v>
+        <v>-14.81330987148237</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.511712607796968</v>
       </c>
       <c r="E46">
-        <v>-31.22437830494965</v>
+        <v>-32.43649003597573</v>
       </c>
       <c r="F46">
-        <v>-1.933963843174027</v>
+        <v>-1.838803481042628</v>
       </c>
       <c r="G46">
-        <v>-13.21362576827096</v>
+        <v>-14.71457299292634</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.513326990073011</v>
       </c>
       <c r="E47">
-        <v>-30.8718343392155</v>
+        <v>-31.89090175176861</v>
       </c>
       <c r="F47">
-        <v>-1.837324845228631</v>
+        <v>-1.68007254768559</v>
       </c>
       <c r="G47">
-        <v>-13.96448082260493</v>
+        <v>-15.12224508435798</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.558563457374426</v>
       </c>
       <c r="E48">
-        <v>-30.94285213284079</v>
+        <v>-31.46059709461175</v>
       </c>
       <c r="F48">
-        <v>-1.796016647953228</v>
+        <v>-1.653017239942755</v>
       </c>
       <c r="G48">
-        <v>-13.84975783261129</v>
+        <v>-14.79246591152599</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.629307360527045</v>
       </c>
       <c r="E49">
-        <v>-29.81994907552881</v>
+        <v>-32.03425059648141</v>
       </c>
       <c r="F49">
-        <v>-1.831156821547386</v>
+        <v>-2.086117539352837</v>
       </c>
       <c r="G49">
-        <v>-13.33641236024694</v>
+        <v>-14.18753498299442</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.723964981991708</v>
       </c>
       <c r="E50">
-        <v>-29.58613943403878</v>
+        <v>-30.99614547920006</v>
       </c>
       <c r="F50">
-        <v>-1.901915965094519</v>
+        <v>-1.845649937626766</v>
       </c>
       <c r="G50">
-        <v>-13.72377697144719</v>
+        <v>-14.60188271968877</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.835260791941042</v>
       </c>
       <c r="E51">
-        <v>-28.89324668307316</v>
+        <v>-30.87695151484417</v>
       </c>
       <c r="F51">
-        <v>-1.763411278611636</v>
+        <v>-2.281828450305651</v>
       </c>
       <c r="G51">
-        <v>-14.25759890695325</v>
+        <v>-14.76086446668698</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.936517815216662</v>
       </c>
       <c r="E52">
-        <v>-28.97628983942582</v>
+        <v>-30.13290738572491</v>
       </c>
       <c r="F52">
-        <v>-1.660102266338899</v>
+        <v>-1.772944130683053</v>
       </c>
       <c r="G52">
-        <v>-14.17583742813501</v>
+        <v>-14.60923101537114</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.02667100840993</v>
       </c>
       <c r="E53">
-        <v>-28.18624773557364</v>
+        <v>-30.45434526350036</v>
       </c>
       <c r="F53">
-        <v>-1.821858397450961</v>
+        <v>-1.556463563839847</v>
       </c>
       <c r="G53">
-        <v>-13.88917350659412</v>
+        <v>-14.79730899454773</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.0942024889489</v>
       </c>
       <c r="E54">
-        <v>-27.7421357611674</v>
+        <v>-30.39248630855558</v>
       </c>
       <c r="F54">
-        <v>-1.835847866149439</v>
+        <v>-2.065528467556256</v>
       </c>
       <c r="G54">
-        <v>-14.22745760570819</v>
+        <v>-14.45132879026598</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.11899789583492</v>
       </c>
       <c r="E55">
-        <v>-27.37081900643446</v>
+        <v>-29.65483412049814</v>
       </c>
       <c r="F55">
-        <v>-1.889674351615948</v>
+        <v>-2.565164065126597</v>
       </c>
       <c r="G55">
-        <v>-14.14624409089037</v>
+        <v>-15.16302574650954</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.1085858771624</v>
       </c>
       <c r="E56">
-        <v>-27.12773505017672</v>
+        <v>-29.74717196975154</v>
       </c>
       <c r="F56">
-        <v>-1.803382490898921</v>
+        <v>-1.906299685390134</v>
       </c>
       <c r="G56">
-        <v>-14.15560705661025</v>
+        <v>-14.97698540592137</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.05674304663039</v>
       </c>
       <c r="E57">
-        <v>-26.93714969308991</v>
+        <v>-29.22823601931657</v>
       </c>
       <c r="F57">
-        <v>-2.066216840867982</v>
+        <v>-2.163275821086597</v>
       </c>
       <c r="G57">
-        <v>-14.32654885619264</v>
+        <v>-14.76998462201146</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.957732777675059</v>
       </c>
       <c r="E58">
-        <v>-26.35318938437879</v>
+        <v>-28.24684324627028</v>
       </c>
       <c r="F58">
-        <v>-1.856951354103159</v>
+        <v>-2.20631199276424</v>
       </c>
       <c r="G58">
-        <v>-14.6244936174549</v>
+        <v>-14.58683831883871</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.825719908471591</v>
       </c>
       <c r="E59">
-        <v>-26.34948509264052</v>
+        <v>-28.27130153438571</v>
       </c>
       <c r="F59">
-        <v>-2.07583004457747</v>
+        <v>-1.893843524754238</v>
       </c>
       <c r="G59">
-        <v>-14.84618443028644</v>
+        <v>-15.65476437490494</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.657571866325112</v>
       </c>
       <c r="E60">
-        <v>-25.69253031139977</v>
+        <v>-26.77152528473338</v>
       </c>
       <c r="F60">
-        <v>-1.944091463040653</v>
+        <v>-2.214359582082437</v>
       </c>
       <c r="G60">
-        <v>-14.66836519031545</v>
+        <v>-15.3210411737585</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.458729895915695</v>
       </c>
       <c r="E61">
-        <v>-25.74273750272281</v>
+        <v>-27.28076124384392</v>
       </c>
       <c r="F61">
-        <v>-2.145905785017294</v>
+        <v>-2.423881034374724</v>
       </c>
       <c r="G61">
-        <v>-14.94311827759556</v>
+        <v>-15.81425963307721</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.244011966160674</v>
       </c>
       <c r="E62">
-        <v>-25.37007579120959</v>
+        <v>-28.08431178566098</v>
       </c>
       <c r="F62">
-        <v>-2.107185407508237</v>
+        <v>-2.104947987153276</v>
       </c>
       <c r="G62">
-        <v>-14.96882664851381</v>
+        <v>-15.72649023758363</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.010429719091242</v>
       </c>
       <c r="E63">
-        <v>-25.58496093982156</v>
+        <v>-27.18430927595455</v>
       </c>
       <c r="F63">
-        <v>-2.21345500487858</v>
+        <v>-2.213728366121504</v>
       </c>
       <c r="G63">
-        <v>-14.82045309081728</v>
+        <v>-16.17179958091289</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.769504666469439</v>
       </c>
       <c r="E64">
-        <v>-25.12848170290038</v>
+        <v>-26.31423997943882</v>
       </c>
       <c r="F64">
-        <v>-2.275538656616194</v>
+        <v>-2.092327809771625</v>
       </c>
       <c r="G64">
-        <v>-15.47672201186792</v>
+        <v>-16.72666891211201</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.53027335018202</v>
       </c>
       <c r="E65">
-        <v>-24.76324668875974</v>
+        <v>-26.82793648544692</v>
       </c>
       <c r="F65">
-        <v>-2.250425042065522</v>
+        <v>-2.226386648403683</v>
       </c>
       <c r="G65">
-        <v>-15.12193172769906</v>
+        <v>-16.36274534773243</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.284738009333511</v>
       </c>
       <c r="E66">
-        <v>-25.04643481082941</v>
+        <v>-26.46306827770091</v>
       </c>
       <c r="F66">
-        <v>-2.582215179745822</v>
+        <v>-2.254180859869815</v>
       </c>
       <c r="G66">
-        <v>-15.13126680303568</v>
+        <v>-15.58165055550662</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.043050312146601</v>
       </c>
       <c r="E67">
-        <v>-24.38311299513387</v>
+        <v>-27.38401950816682</v>
       </c>
       <c r="F67">
-        <v>-2.639727900154789</v>
+        <v>-2.464826406727701</v>
       </c>
       <c r="G67">
-        <v>-14.88986569229655</v>
+        <v>-15.24108108557639</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.804462986817284</v>
       </c>
       <c r="E68">
-        <v>-24.18599305005398</v>
+        <v>-26.92888522802591</v>
       </c>
       <c r="F68">
-        <v>-2.436360389297899</v>
+        <v>-2.465555370042165</v>
       </c>
       <c r="G68">
-        <v>-15.39603841433195</v>
+        <v>-16.79954812416883</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.557315835449919</v>
       </c>
       <c r="E69">
-        <v>-23.85456762285461</v>
+        <v>-28.34199554211945</v>
       </c>
       <c r="F69">
-        <v>-2.454030294367015</v>
+        <v>-2.457289920097031</v>
       </c>
       <c r="G69">
-        <v>-15.47853980861185</v>
+        <v>-15.27242331391221</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.308723958190593</v>
       </c>
       <c r="E70">
-        <v>-24.17309595608014</v>
+        <v>-26.3824161556243</v>
       </c>
       <c r="F70">
-        <v>-2.768166265958852</v>
+        <v>-2.752555682253095</v>
       </c>
       <c r="G70">
-        <v>-15.29267173215554</v>
+        <v>-15.49926236337052</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.052229059015485</v>
       </c>
       <c r="E71">
-        <v>-24.23238726626257</v>
+        <v>-26.22149683176173</v>
       </c>
       <c r="F71">
-        <v>-2.727934117939686</v>
+        <v>-2.463756156043284</v>
       </c>
       <c r="G71">
-        <v>-15.17814069362312</v>
+        <v>-16.42439621961284</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.778602309406206</v>
       </c>
       <c r="E72">
-        <v>-24.08477712750854</v>
+        <v>-25.58648703556215</v>
       </c>
       <c r="F72">
-        <v>-2.837152703263995</v>
+        <v>-2.408595170690865</v>
       </c>
       <c r="G72">
-        <v>-15.03978962717992</v>
+        <v>-15.47015792813825</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.495149246884015</v>
       </c>
       <c r="E73">
-        <v>-24.69173302723061</v>
+        <v>-25.62893695091005</v>
       </c>
       <c r="F73">
-        <v>-3.01802175546085</v>
+        <v>-3.08531169632506</v>
       </c>
       <c r="G73">
-        <v>-14.63813857730985</v>
+        <v>-16.42173843014969</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.196467156651702</v>
       </c>
       <c r="E74">
-        <v>-24.53926383586636</v>
+        <v>-26.59692996936764</v>
       </c>
       <c r="F74">
-        <v>-3.059484029073174</v>
+        <v>-3.158211341241027</v>
       </c>
       <c r="G74">
-        <v>-15.25524611904852</v>
+        <v>-15.22117227376446</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.883784351047005</v>
       </c>
       <c r="E75">
-        <v>-24.76216438347191</v>
+        <v>-26.73697755652886</v>
       </c>
       <c r="F75">
-        <v>-3.02693995891939</v>
+        <v>-3.079862695549445</v>
       </c>
       <c r="G75">
-        <v>-14.91241096563149</v>
+        <v>-14.9432199954639</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.56743892932516</v>
       </c>
       <c r="E76">
-        <v>-25.07649482129232</v>
+        <v>-26.95275481452034</v>
       </c>
       <c r="F76">
-        <v>-3.004973312131952</v>
+        <v>-3.3379314478502</v>
       </c>
       <c r="G76">
-        <v>-14.60223545100641</v>
+        <v>-16.01273580337568</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.246472033116786</v>
       </c>
       <c r="E77">
-        <v>-24.9016685537522</v>
+        <v>-27.34665054065552</v>
       </c>
       <c r="F77">
-        <v>-3.101151737801392</v>
+        <v>-3.274553886229412</v>
       </c>
       <c r="G77">
-        <v>-14.51662017746659</v>
+        <v>-14.96807688938747</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.92957867324635</v>
       </c>
       <c r="E78">
-        <v>-25.14946665145192</v>
+        <v>-28.00640844730703</v>
       </c>
       <c r="F78">
-        <v>-3.064146909183532</v>
+        <v>-3.634805071135097</v>
       </c>
       <c r="G78">
-        <v>-14.10565209897848</v>
+        <v>-14.5437968950327</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.6253581106593</v>
       </c>
       <c r="E79">
-        <v>-25.75561195432661</v>
+        <v>-28.13335063069004</v>
       </c>
       <c r="F79">
-        <v>-3.363188369961557</v>
+        <v>-3.083518280897999</v>
       </c>
       <c r="G79">
-        <v>-14.05119038353482</v>
+        <v>-14.85581809678497</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.331646408637677</v>
       </c>
       <c r="E80">
-        <v>-25.83625954792922</v>
+        <v>-28.65583237627303</v>
       </c>
       <c r="F80">
-        <v>-3.257284910983251</v>
+        <v>-3.46234477644406</v>
       </c>
       <c r="G80">
-        <v>-13.37063878233351</v>
+        <v>-14.35152059287079</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.058999605657166</v>
       </c>
       <c r="E81">
-        <v>-26.61186487664494</v>
+        <v>-28.83870121365077</v>
       </c>
       <c r="F81">
-        <v>-3.205714069954565</v>
+        <v>-3.508880800398531</v>
       </c>
       <c r="G81">
-        <v>-13.30750807952979</v>
+        <v>-14.35978270875748</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.811959077174947</v>
       </c>
       <c r="E82">
-        <v>-26.97537454218866</v>
+        <v>-28.98640192188495</v>
       </c>
       <c r="F82">
-        <v>-3.239680446938956</v>
+        <v>-3.135856190141677</v>
       </c>
       <c r="G82">
-        <v>-12.95865188455119</v>
+        <v>-13.08878185037721</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.587483127399305</v>
       </c>
       <c r="E83">
-        <v>-27.43452557877437</v>
+        <v>-30.42539925764333</v>
       </c>
       <c r="F83">
-        <v>-3.389953749113412</v>
+        <v>-3.459751158105895</v>
       </c>
       <c r="G83">
-        <v>-12.72442516475179</v>
+        <v>-13.3196682866291</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.395579108889508</v>
       </c>
       <c r="E84">
-        <v>-28.12188906297663</v>
+        <v>-29.72848295752189</v>
       </c>
       <c r="F84">
-        <v>-3.509391903086058</v>
+        <v>-3.46606414608263</v>
       </c>
       <c r="G84">
-        <v>-12.85079156944912</v>
+        <v>-13.55990948554696</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.237727613415411</v>
       </c>
       <c r="E85">
-        <v>-28.96138210299257</v>
+        <v>-31.14652025133577</v>
       </c>
       <c r="F85">
-        <v>-3.471899994435352</v>
+        <v>-4.074529824665367</v>
       </c>
       <c r="G85">
-        <v>-12.58549496270334</v>
+        <v>-12.36736263465301</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.112113067837737</v>
       </c>
       <c r="E86">
-        <v>-30.16890875408588</v>
+        <v>-32.52800823143374</v>
       </c>
       <c r="F86">
-        <v>-3.476310222487857</v>
+        <v>-4.12736889618774</v>
       </c>
       <c r="G86">
-        <v>-12.23849593912738</v>
+        <v>-12.69598353627452</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.028556501908637</v>
       </c>
       <c r="E87">
-        <v>-30.58171085920309</v>
+        <v>-32.82178845420735</v>
       </c>
       <c r="F87">
-        <v>-3.528063304345159</v>
+        <v>-3.873443637635788</v>
       </c>
       <c r="G87">
-        <v>-11.88541024955866</v>
+        <v>-13.43730992319987</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.985429396130501</v>
       </c>
       <c r="E88">
-        <v>-31.85443621482184</v>
+        <v>-34.39954276203476</v>
       </c>
       <c r="F88">
-        <v>-3.554148593859316</v>
+        <v>-3.320254915841861</v>
       </c>
       <c r="G88">
-        <v>-12.13708322438963</v>
+        <v>-13.05049327600005</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.982908649118015</v>
       </c>
       <c r="E89">
-        <v>-32.44250611369492</v>
+        <v>-36.0548358660585</v>
       </c>
       <c r="F89">
-        <v>-3.738843875089702</v>
+        <v>-3.687767569400487</v>
       </c>
       <c r="G89">
-        <v>-11.64705575303747</v>
+        <v>-12.93929923979359</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.027232587624281</v>
       </c>
       <c r="E90">
-        <v>-34.15382549814156</v>
+        <v>-36.37869421319105</v>
       </c>
       <c r="F90">
-        <v>-3.801783230354408</v>
+        <v>-3.619050351501254</v>
       </c>
       <c r="G90">
-        <v>-11.65236476952066</v>
+        <v>-12.49872633978539</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.112337115122712</v>
       </c>
       <c r="E91">
-        <v>-35.2452964173663</v>
+        <v>-36.65933506863141</v>
       </c>
       <c r="F91">
-        <v>-4.067906198912583</v>
+        <v>-3.743525807650324</v>
       </c>
       <c r="G91">
-        <v>-11.50282637817052</v>
+        <v>-12.56865901488183</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.239195404379261</v>
       </c>
       <c r="E92">
-        <v>-36.45280495456359</v>
+        <v>-38.29037366587007</v>
       </c>
       <c r="F92">
-        <v>-3.917253504467645</v>
+        <v>-3.93732567500488</v>
       </c>
       <c r="G92">
-        <v>-11.24095864795436</v>
+        <v>-12.83026424737324</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.408254225466731</v>
       </c>
       <c r="E93">
-        <v>-38.1752666493061</v>
+        <v>-39.42556020892786</v>
       </c>
       <c r="F93">
-        <v>-4.018275394341253</v>
+        <v>-3.754892665151539</v>
       </c>
       <c r="G93">
-        <v>-12.05506581028975</v>
+        <v>-13.16789538339698</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.609096414850972</v>
       </c>
       <c r="E94">
-        <v>-40.03788687882302</v>
+        <v>-41.21789172913472</v>
       </c>
       <c r="F94">
-        <v>-4.290009723685992</v>
+        <v>-4.510306579153895</v>
       </c>
       <c r="G94">
-        <v>-11.94441645686215</v>
+        <v>-13.27146386069929</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.841658034716935</v>
       </c>
       <c r="E95">
-        <v>-40.6443786099593</v>
+        <v>-42.04873991227002</v>
       </c>
       <c r="F95">
-        <v>-4.272875772326487</v>
+        <v>-4.275851268037343</v>
       </c>
       <c r="G95">
-        <v>-12.51172325838234</v>
+        <v>-12.64316571283214</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.101174212480363</v>
       </c>
       <c r="E96">
-        <v>-42.95652234032163</v>
+        <v>-45.39083524246288</v>
       </c>
       <c r="F96">
-        <v>-4.561840972016858</v>
+        <v>-4.458738223227417</v>
       </c>
       <c r="G96">
-        <v>-12.46751207909039</v>
+        <v>-13.173443929054</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.371367518829033</v>
       </c>
       <c r="E97">
-        <v>-44.27378297356881</v>
+        <v>-46.31801765316334</v>
       </c>
       <c r="F97">
-        <v>-4.527871281562856</v>
+        <v>-4.116981168956634</v>
       </c>
       <c r="G97">
-        <v>-12.916304439105</v>
+        <v>-13.47131650344195</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.65133224217624</v>
       </c>
       <c r="E98">
-        <v>-45.5453535683156</v>
+        <v>-47.35393778173599</v>
       </c>
       <c r="F98">
-        <v>-4.551662821738661</v>
+        <v>-4.693729488053581</v>
       </c>
       <c r="G98">
-        <v>-13.02699316719131</v>
+        <v>-13.40844829836299</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.922010536887928</v>
       </c>
       <c r="E99">
-        <v>-47.67921354123295</v>
+        <v>-48.25437502494716</v>
       </c>
       <c r="F99">
-        <v>-4.764074447899315</v>
+        <v>-4.997814877947252</v>
       </c>
       <c r="G99">
-        <v>-12.96692712532411</v>
+        <v>-14.45237714055423</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.175623411372809</v>
       </c>
       <c r="E100">
-        <v>-49.44315266153022</v>
+        <v>-50.93615544618557</v>
       </c>
       <c r="F100">
-        <v>-4.989928820272601</v>
+        <v>-4.647115597563247</v>
       </c>
       <c r="G100">
-        <v>-13.77105773350801</v>
+        <v>-13.70791554642883</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.388178814092345</v>
       </c>
       <c r="E101">
-        <v>-51.61291437638037</v>
+        <v>-51.90629835767831</v>
       </c>
       <c r="F101">
-        <v>-4.980065449607467</v>
+        <v>-5.12349975050441</v>
       </c>
       <c r="G101">
-        <v>-13.8047640819774</v>
+        <v>-14.51014304610825</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.567278277800566</v>
       </c>
       <c r="E102">
-        <v>-53.04758815157993</v>
+        <v>-53.45452814709421</v>
       </c>
       <c r="F102">
-        <v>-5.212566642020815</v>
+        <v>-4.821700654642465</v>
       </c>
       <c r="G102">
-        <v>-13.942225937378</v>
+        <v>-14.82288283538204</v>
       </c>
     </row>
   </sheetData>
